--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808181</v>
+        <v>124808124</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465621</v>
+        <v>465636</v>
       </c>
       <c r="R2" t="n">
-        <v>7054698</v>
+        <v>7054718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808201</v>
+        <v>124808176</v>
       </c>
       <c r="B4" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465645</v>
+        <v>465516</v>
       </c>
       <c r="R4" t="n">
-        <v>7054657</v>
+        <v>7054331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808167</v>
+        <v>124808171</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465559</v>
+        <v>465504</v>
       </c>
       <c r="R5" t="n">
-        <v>7054552</v>
+        <v>7054411</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808171</v>
+        <v>124808200</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465504</v>
+        <v>465674</v>
       </c>
       <c r="R6" t="n">
-        <v>7054411</v>
+        <v>7054729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808173</v>
+        <v>124808174</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465503</v>
+        <v>465485</v>
       </c>
       <c r="R7" t="n">
-        <v>7054351</v>
+        <v>7054334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1275,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808164</v>
+        <v>124808170</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465655</v>
+        <v>465511</v>
       </c>
       <c r="R8" t="n">
-        <v>7054664</v>
+        <v>7054408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808177</v>
+        <v>124808169</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465517</v>
+        <v>465536</v>
       </c>
       <c r="R9" t="n">
-        <v>7054325</v>
+        <v>7054410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808169</v>
+        <v>124808172</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465536</v>
+        <v>465497</v>
       </c>
       <c r="R10" t="n">
-        <v>7054410</v>
+        <v>7054413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808198</v>
+        <v>124808164</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465568</v>
+        <v>465655</v>
       </c>
       <c r="R12" t="n">
-        <v>7054466</v>
+        <v>7054664</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1806,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808199</v>
+        <v>124808173</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465617</v>
+        <v>465503</v>
       </c>
       <c r="R13" t="n">
-        <v>7054717</v>
+        <v>7054351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808197</v>
+        <v>124808201</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465565</v>
+        <v>465645</v>
       </c>
       <c r="R14" t="n">
-        <v>7054514</v>
+        <v>7054657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808172</v>
+        <v>124808165</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465497</v>
+        <v>465638</v>
       </c>
       <c r="R15" t="n">
-        <v>7054413</v>
+        <v>7054579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808174</v>
+        <v>124808177</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465485</v>
+        <v>465517</v>
       </c>
       <c r="R16" t="n">
-        <v>7054334</v>
+        <v>7054325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808180</v>
+        <v>124808181</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465470</v>
+        <v>465621</v>
       </c>
       <c r="R17" t="n">
-        <v>7054306</v>
+        <v>7054698</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808170</v>
+        <v>124808199</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465511</v>
+        <v>465617</v>
       </c>
       <c r="R18" t="n">
-        <v>7054408</v>
+        <v>7054717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808200</v>
+        <v>124808197</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465674</v>
+        <v>465565</v>
       </c>
       <c r="R19" t="n">
-        <v>7054729</v>
+        <v>7054514</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808124</v>
+        <v>124808167</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465636</v>
+        <v>465559</v>
       </c>
       <c r="R21" t="n">
-        <v>7054718</v>
+        <v>7054552</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2754,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808168</v>
+        <v>124808198</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465537</v>
+        <v>465568</v>
       </c>
       <c r="R22" t="n">
-        <v>7054390</v>
+        <v>7054466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2856,11 +2861,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808176</v>
+        <v>124808180</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465516</v>
+        <v>465470</v>
       </c>
       <c r="R23" t="n">
-        <v>7054331</v>
+        <v>7054306</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808165</v>
+        <v>124808168</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465638</v>
+        <v>465537</v>
       </c>
       <c r="R24" t="n">
-        <v>7054579</v>
+        <v>7054390</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808124</v>
+        <v>124808169</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465636</v>
+        <v>465536</v>
       </c>
       <c r="R2" t="n">
-        <v>7054718</v>
+        <v>7054410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808196</v>
+        <v>124808197</v>
       </c>
       <c r="B3" t="n">
         <v>91030</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465573</v>
+        <v>465565</v>
       </c>
       <c r="R3" t="n">
-        <v>7054561</v>
+        <v>7054514</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808176</v>
+        <v>124808201</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465516</v>
+        <v>465645</v>
       </c>
       <c r="R4" t="n">
-        <v>7054331</v>
+        <v>7054657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808171</v>
+        <v>124808177</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465504</v>
+        <v>465517</v>
       </c>
       <c r="R5" t="n">
-        <v>7054411</v>
+        <v>7054325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808200</v>
+        <v>124808181</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465674</v>
+        <v>465621</v>
       </c>
       <c r="R6" t="n">
-        <v>7054729</v>
+        <v>7054698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808174</v>
+        <v>124808124</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465485</v>
+        <v>465636</v>
       </c>
       <c r="R7" t="n">
-        <v>7054334</v>
+        <v>7054718</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808170</v>
+        <v>124808199</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465511</v>
+        <v>465617</v>
       </c>
       <c r="R8" t="n">
-        <v>7054408</v>
+        <v>7054717</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808169</v>
+        <v>124808170</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465536</v>
+        <v>465511</v>
       </c>
       <c r="R9" t="n">
-        <v>7054410</v>
+        <v>7054408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808163</v>
+        <v>124808186</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465656</v>
+        <v>465644</v>
       </c>
       <c r="R11" t="n">
-        <v>7054667</v>
+        <v>7054651</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808173</v>
+        <v>124808198</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465503</v>
+        <v>465568</v>
       </c>
       <c r="R13" t="n">
-        <v>7054351</v>
+        <v>7054466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808201</v>
+        <v>124808173</v>
       </c>
       <c r="B14" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465645</v>
+        <v>465503</v>
       </c>
       <c r="R14" t="n">
-        <v>7054657</v>
+        <v>7054351</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2010,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808165</v>
+        <v>124808171</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465638</v>
+        <v>465504</v>
       </c>
       <c r="R15" t="n">
-        <v>7054579</v>
+        <v>7054411</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2153,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808177</v>
+        <v>124808176</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465517</v>
+        <v>465516</v>
       </c>
       <c r="R16" t="n">
-        <v>7054325</v>
+        <v>7054331</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808181</v>
+        <v>124808196</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465621</v>
+        <v>465573</v>
       </c>
       <c r="R17" t="n">
-        <v>7054698</v>
+        <v>7054561</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808199</v>
+        <v>124808180</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465617</v>
+        <v>465470</v>
       </c>
       <c r="R18" t="n">
-        <v>7054717</v>
+        <v>7054306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808197</v>
+        <v>124808167</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465565</v>
+        <v>465559</v>
       </c>
       <c r="R19" t="n">
-        <v>7054514</v>
+        <v>7054552</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808186</v>
+        <v>124808163</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465644</v>
+        <v>465656</v>
       </c>
       <c r="R20" t="n">
-        <v>7054651</v>
+        <v>7054667</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,6 +2647,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808167</v>
+        <v>124808165</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465559</v>
+        <v>465638</v>
       </c>
       <c r="R21" t="n">
-        <v>7054552</v>
+        <v>7054579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808198</v>
+        <v>124808200</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465568</v>
+        <v>465674</v>
       </c>
       <c r="R22" t="n">
-        <v>7054466</v>
+        <v>7054729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808180</v>
+        <v>124808174</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465470</v>
+        <v>465485</v>
       </c>
       <c r="R23" t="n">
-        <v>7054306</v>
+        <v>7054334</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808201</v>
+        <v>124808177</v>
       </c>
       <c r="B4" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465645</v>
+        <v>465517</v>
       </c>
       <c r="R4" t="n">
-        <v>7054657</v>
+        <v>7054325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808177</v>
+        <v>124808181</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465517</v>
+        <v>465621</v>
       </c>
       <c r="R5" t="n">
-        <v>7054325</v>
+        <v>7054698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808181</v>
+        <v>124808201</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465621</v>
+        <v>465645</v>
       </c>
       <c r="R6" t="n">
-        <v>7054698</v>
+        <v>7054657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808186</v>
+        <v>124808164</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465644</v>
+        <v>465655</v>
       </c>
       <c r="R11" t="n">
-        <v>7054651</v>
+        <v>7054664</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808164</v>
+        <v>124808186</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465655</v>
+        <v>465644</v>
       </c>
       <c r="R12" t="n">
-        <v>7054664</v>
+        <v>7054651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808165</v>
+        <v>124808200</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465638</v>
+        <v>465674</v>
       </c>
       <c r="R21" t="n">
-        <v>7054579</v>
+        <v>7054729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,11 +2754,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2780,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808200</v>
+        <v>124808165</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2796,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465674</v>
+        <v>465638</v>
       </c>
       <c r="R22" t="n">
-        <v>7054729</v>
+        <v>7054579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,6 +2856,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808177</v>
+        <v>124808201</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465517</v>
+        <v>465645</v>
       </c>
       <c r="R4" t="n">
-        <v>7054325</v>
+        <v>7054657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808181</v>
+        <v>124808177</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465621</v>
+        <v>465517</v>
       </c>
       <c r="R5" t="n">
-        <v>7054698</v>
+        <v>7054325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808201</v>
+        <v>124808181</v>
       </c>
       <c r="B6" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465645</v>
+        <v>465621</v>
       </c>
       <c r="R6" t="n">
-        <v>7054657</v>
+        <v>7054698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808164</v>
+        <v>124808186</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465655</v>
+        <v>465644</v>
       </c>
       <c r="R11" t="n">
-        <v>7054664</v>
+        <v>7054651</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808186</v>
+        <v>124808164</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465644</v>
+        <v>465655</v>
       </c>
       <c r="R12" t="n">
-        <v>7054651</v>
+        <v>7054664</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808197</v>
+        <v>124808171</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465565</v>
+        <v>465504</v>
       </c>
       <c r="R3" t="n">
-        <v>7054514</v>
+        <v>7054411</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808201</v>
+        <v>124808199</v>
       </c>
       <c r="B4" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465645</v>
+        <v>465617</v>
       </c>
       <c r="R4" t="n">
-        <v>7054657</v>
+        <v>7054717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808177</v>
+        <v>124808200</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465517</v>
+        <v>465674</v>
       </c>
       <c r="R5" t="n">
-        <v>7054325</v>
+        <v>7054729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808181</v>
+        <v>124808186</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465621</v>
+        <v>465644</v>
       </c>
       <c r="R6" t="n">
-        <v>7054698</v>
+        <v>7054651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808124</v>
+        <v>124808172</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465636</v>
+        <v>465497</v>
       </c>
       <c r="R7" t="n">
-        <v>7054718</v>
+        <v>7054413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808199</v>
+        <v>124808168</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465617</v>
+        <v>465537</v>
       </c>
       <c r="R8" t="n">
-        <v>7054717</v>
+        <v>7054390</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808170</v>
+        <v>124808197</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465511</v>
+        <v>465565</v>
       </c>
       <c r="R9" t="n">
-        <v>7054408</v>
+        <v>7054514</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808172</v>
+        <v>124808167</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465497</v>
+        <v>465559</v>
       </c>
       <c r="R10" t="n">
-        <v>7054413</v>
+        <v>7054552</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808186</v>
+        <v>124808198</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465644</v>
+        <v>465568</v>
       </c>
       <c r="R11" t="n">
-        <v>7054651</v>
+        <v>7054466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808164</v>
+        <v>124808165</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465655</v>
+        <v>465638</v>
       </c>
       <c r="R12" t="n">
-        <v>7054664</v>
+        <v>7054579</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808198</v>
+        <v>124808201</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465568</v>
+        <v>465645</v>
       </c>
       <c r="R13" t="n">
-        <v>7054466</v>
+        <v>7054657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808173</v>
+        <v>124808124</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465503</v>
+        <v>465636</v>
       </c>
       <c r="R14" t="n">
-        <v>7054351</v>
+        <v>7054718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808171</v>
+        <v>124808176</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2081,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465504</v>
+        <v>465516</v>
       </c>
       <c r="R15" t="n">
-        <v>7054411</v>
+        <v>7054331</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2143,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808176</v>
+        <v>124808174</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465516</v>
+        <v>465485</v>
       </c>
       <c r="R16" t="n">
-        <v>7054331</v>
+        <v>7054334</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2255,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808196</v>
+        <v>124808164</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465573</v>
+        <v>465655</v>
       </c>
       <c r="R17" t="n">
-        <v>7054561</v>
+        <v>7054664</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2326,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808180</v>
+        <v>124808173</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465470</v>
+        <v>465503</v>
       </c>
       <c r="R18" t="n">
-        <v>7054306</v>
+        <v>7054351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808167</v>
+        <v>124808170</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465559</v>
+        <v>465511</v>
       </c>
       <c r="R19" t="n">
-        <v>7054552</v>
+        <v>7054408</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808163</v>
+        <v>124808177</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465656</v>
+        <v>465517</v>
       </c>
       <c r="R20" t="n">
-        <v>7054667</v>
+        <v>7054325</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808200</v>
+        <v>124808180</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465674</v>
+        <v>465470</v>
       </c>
       <c r="R21" t="n">
-        <v>7054729</v>
+        <v>7054306</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2754,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808165</v>
+        <v>124808181</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465638</v>
+        <v>465621</v>
       </c>
       <c r="R22" t="n">
-        <v>7054579</v>
+        <v>7054698</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808174</v>
+        <v>124808196</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465485</v>
+        <v>465573</v>
       </c>
       <c r="R23" t="n">
-        <v>7054334</v>
+        <v>7054561</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,11 +2968,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,7 +2994,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808168</v>
+        <v>124808163</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465537</v>
+        <v>465656</v>
       </c>
       <c r="R24" t="n">
-        <v>7054390</v>
+        <v>7054667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808169</v>
+        <v>124808164</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465536</v>
+        <v>465655</v>
       </c>
       <c r="R2" t="n">
-        <v>7054410</v>
+        <v>7054664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808171</v>
+        <v>124808176</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465504</v>
+        <v>465516</v>
       </c>
       <c r="R3" t="n">
-        <v>7054411</v>
+        <v>7054331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808199</v>
+        <v>124808171</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465617</v>
+        <v>465504</v>
       </c>
       <c r="R4" t="n">
-        <v>7054717</v>
+        <v>7054411</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808200</v>
+        <v>124808124</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465674</v>
+        <v>465636</v>
       </c>
       <c r="R5" t="n">
-        <v>7054729</v>
+        <v>7054718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808186</v>
+        <v>124808196</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465644</v>
+        <v>465573</v>
       </c>
       <c r="R6" t="n">
-        <v>7054651</v>
+        <v>7054561</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808172</v>
+        <v>124808200</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465497</v>
+        <v>465674</v>
       </c>
       <c r="R7" t="n">
-        <v>7054413</v>
+        <v>7054729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808168</v>
+        <v>124808174</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465537</v>
+        <v>465485</v>
       </c>
       <c r="R8" t="n">
-        <v>7054390</v>
+        <v>7054334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808197</v>
+        <v>124808170</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465565</v>
+        <v>465511</v>
       </c>
       <c r="R9" t="n">
-        <v>7054514</v>
+        <v>7054408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808167</v>
+        <v>124808180</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465559</v>
+        <v>465470</v>
       </c>
       <c r="R10" t="n">
-        <v>7054552</v>
+        <v>7054306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808198</v>
+        <v>124808177</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465568</v>
+        <v>465517</v>
       </c>
       <c r="R11" t="n">
-        <v>7054466</v>
+        <v>7054325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808165</v>
+        <v>124808198</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465638</v>
+        <v>465568</v>
       </c>
       <c r="R12" t="n">
-        <v>7054579</v>
+        <v>7054466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808201</v>
+        <v>124808199</v>
       </c>
       <c r="B13" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465645</v>
+        <v>465617</v>
       </c>
       <c r="R13" t="n">
-        <v>7054657</v>
+        <v>7054717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808124</v>
+        <v>124808165</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465636</v>
+        <v>465638</v>
       </c>
       <c r="R14" t="n">
-        <v>7054718</v>
+        <v>7054579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808176</v>
+        <v>124808181</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2076,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465516</v>
+        <v>465621</v>
       </c>
       <c r="R15" t="n">
-        <v>7054331</v>
+        <v>7054698</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808174</v>
+        <v>124808186</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465485</v>
+        <v>465644</v>
       </c>
       <c r="R16" t="n">
-        <v>7054334</v>
+        <v>7054651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808164</v>
+        <v>124808167</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465655</v>
+        <v>465559</v>
       </c>
       <c r="R17" t="n">
-        <v>7054664</v>
+        <v>7054552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808173</v>
+        <v>124808201</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465503</v>
+        <v>465645</v>
       </c>
       <c r="R18" t="n">
-        <v>7054351</v>
+        <v>7054657</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808170</v>
+        <v>124808173</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465511</v>
+        <v>465503</v>
       </c>
       <c r="R19" t="n">
-        <v>7054408</v>
+        <v>7054351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808177</v>
+        <v>124808169</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465517</v>
+        <v>465536</v>
       </c>
       <c r="R20" t="n">
-        <v>7054325</v>
+        <v>7054410</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808180</v>
+        <v>124808168</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465470</v>
+        <v>465537</v>
       </c>
       <c r="R21" t="n">
-        <v>7054306</v>
+        <v>7054390</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808181</v>
+        <v>124808172</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465621</v>
+        <v>465497</v>
       </c>
       <c r="R22" t="n">
-        <v>7054698</v>
+        <v>7054413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808196</v>
+        <v>124808163</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465573</v>
+        <v>465656</v>
       </c>
       <c r="R23" t="n">
-        <v>7054561</v>
+        <v>7054667</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,6 +2968,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808163</v>
+        <v>124808197</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465656</v>
+        <v>465565</v>
       </c>
       <c r="R24" t="n">
-        <v>7054667</v>
+        <v>7054514</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,11 +3075,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -2255,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808167</v>
+        <v>124808173</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465559</v>
+        <v>465503</v>
       </c>
       <c r="R17" t="n">
-        <v>7054552</v>
+        <v>7054351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808201</v>
+        <v>124808167</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465645</v>
+        <v>465559</v>
       </c>
       <c r="R18" t="n">
-        <v>7054657</v>
+        <v>7054552</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,6 +2438,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808173</v>
+        <v>124808201</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465503</v>
+        <v>465645</v>
       </c>
       <c r="R19" t="n">
-        <v>7054351</v>
+        <v>7054657</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2545,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808164</v>
+        <v>124808198</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465655</v>
+        <v>465568</v>
       </c>
       <c r="R2" t="n">
-        <v>7054664</v>
+        <v>7054466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808176</v>
+        <v>124808165</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465516</v>
+        <v>465638</v>
       </c>
       <c r="R3" t="n">
-        <v>7054331</v>
+        <v>7054579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808171</v>
+        <v>124808168</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465504</v>
+        <v>465537</v>
       </c>
       <c r="R4" t="n">
-        <v>7054411</v>
+        <v>7054390</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808124</v>
+        <v>124808180</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465636</v>
+        <v>465470</v>
       </c>
       <c r="R5" t="n">
-        <v>7054718</v>
+        <v>7054306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808196</v>
+        <v>124808163</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465573</v>
+        <v>465656</v>
       </c>
       <c r="R6" t="n">
-        <v>7054561</v>
+        <v>7054667</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808200</v>
+        <v>124808197</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465674</v>
+        <v>465565</v>
       </c>
       <c r="R7" t="n">
-        <v>7054729</v>
+        <v>7054514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808174</v>
+        <v>124808171</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465485</v>
+        <v>465504</v>
       </c>
       <c r="R8" t="n">
-        <v>7054334</v>
+        <v>7054411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808170</v>
+        <v>124808199</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465511</v>
+        <v>465617</v>
       </c>
       <c r="R9" t="n">
-        <v>7054408</v>
+        <v>7054717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808180</v>
+        <v>124808200</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465470</v>
+        <v>465674</v>
       </c>
       <c r="R10" t="n">
-        <v>7054306</v>
+        <v>7054729</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808177</v>
+        <v>124808124</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465517</v>
+        <v>465636</v>
       </c>
       <c r="R11" t="n">
-        <v>7054325</v>
+        <v>7054718</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808198</v>
+        <v>124808169</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465568</v>
+        <v>465536</v>
       </c>
       <c r="R12" t="n">
-        <v>7054466</v>
+        <v>7054410</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808199</v>
+        <v>124808176</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465617</v>
+        <v>465516</v>
       </c>
       <c r="R13" t="n">
-        <v>7054717</v>
+        <v>7054331</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808165</v>
+        <v>124808177</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465638</v>
+        <v>465517</v>
       </c>
       <c r="R14" t="n">
-        <v>7054579</v>
+        <v>7054325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808181</v>
+        <v>124808172</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465621</v>
+        <v>465497</v>
       </c>
       <c r="R15" t="n">
-        <v>7054698</v>
+        <v>7054413</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808186</v>
+        <v>124808173</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465644</v>
+        <v>465503</v>
       </c>
       <c r="R16" t="n">
-        <v>7054651</v>
+        <v>7054351</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2260,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808173</v>
+        <v>124808167</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2295,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465503</v>
+        <v>465559</v>
       </c>
       <c r="R17" t="n">
-        <v>7054351</v>
+        <v>7054552</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2340,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808167</v>
+        <v>124808196</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465559</v>
+        <v>465573</v>
       </c>
       <c r="R18" t="n">
-        <v>7054552</v>
+        <v>7054561</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,11 +2443,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808201</v>
+        <v>124808186</v>
       </c>
       <c r="B19" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465645</v>
+        <v>465644</v>
       </c>
       <c r="R19" t="n">
-        <v>7054657</v>
+        <v>7054651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808169</v>
+        <v>124808170</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465536</v>
+        <v>465511</v>
       </c>
       <c r="R20" t="n">
-        <v>7054410</v>
+        <v>7054408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808168</v>
+        <v>124808201</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465537</v>
+        <v>465645</v>
       </c>
       <c r="R21" t="n">
-        <v>7054390</v>
+        <v>7054657</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,11 +2754,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808172</v>
+        <v>124808174</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2825,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465497</v>
+        <v>465485</v>
       </c>
       <c r="R22" t="n">
-        <v>7054413</v>
+        <v>7054334</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2860,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,7 +2887,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808163</v>
+        <v>124808181</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2932,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465656</v>
+        <v>465621</v>
       </c>
       <c r="R23" t="n">
-        <v>7054667</v>
+        <v>7054698</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808197</v>
+        <v>124808164</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465565</v>
+        <v>465655</v>
       </c>
       <c r="R24" t="n">
-        <v>7054514</v>
+        <v>7054664</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3070,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808198</v>
+        <v>124808170</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465568</v>
+        <v>465511</v>
       </c>
       <c r="R2" t="n">
-        <v>7054466</v>
+        <v>7054408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808165</v>
+        <v>124808180</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465638</v>
+        <v>465470</v>
       </c>
       <c r="R3" t="n">
-        <v>7054579</v>
+        <v>7054306</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808168</v>
+        <v>124808199</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465537</v>
+        <v>465617</v>
       </c>
       <c r="R4" t="n">
-        <v>7054390</v>
+        <v>7054717</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808180</v>
+        <v>124808196</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465470</v>
+        <v>465573</v>
       </c>
       <c r="R5" t="n">
-        <v>7054306</v>
+        <v>7054561</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808163</v>
+        <v>124808174</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465656</v>
+        <v>465485</v>
       </c>
       <c r="R6" t="n">
-        <v>7054667</v>
+        <v>7054334</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808197</v>
+        <v>124808167</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465565</v>
+        <v>465559</v>
       </c>
       <c r="R7" t="n">
-        <v>7054514</v>
+        <v>7054552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808171</v>
+        <v>124808163</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465504</v>
+        <v>465656</v>
       </c>
       <c r="R8" t="n">
-        <v>7054411</v>
+        <v>7054667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808199</v>
+        <v>124808173</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465617</v>
+        <v>465503</v>
       </c>
       <c r="R9" t="n">
-        <v>7054717</v>
+        <v>7054351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808200</v>
+        <v>124808164</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465674</v>
+        <v>465655</v>
       </c>
       <c r="R10" t="n">
-        <v>7054729</v>
+        <v>7054664</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1602,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808124</v>
+        <v>124808201</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465636</v>
+        <v>465645</v>
       </c>
       <c r="R11" t="n">
-        <v>7054718</v>
+        <v>7054657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808169</v>
+        <v>124808200</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465536</v>
+        <v>465674</v>
       </c>
       <c r="R12" t="n">
-        <v>7054410</v>
+        <v>7054729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808176</v>
+        <v>124808197</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465516</v>
+        <v>465565</v>
       </c>
       <c r="R13" t="n">
-        <v>7054331</v>
+        <v>7054514</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808177</v>
+        <v>124808169</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465517</v>
+        <v>465536</v>
       </c>
       <c r="R14" t="n">
-        <v>7054325</v>
+        <v>7054410</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808172</v>
+        <v>124808186</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465497</v>
+        <v>465644</v>
       </c>
       <c r="R15" t="n">
-        <v>7054413</v>
+        <v>7054651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808173</v>
+        <v>124808181</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465503</v>
+        <v>465621</v>
       </c>
       <c r="R16" t="n">
-        <v>7054351</v>
+        <v>7054698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808167</v>
+        <v>124808198</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465559</v>
+        <v>465568</v>
       </c>
       <c r="R17" t="n">
-        <v>7054552</v>
+        <v>7054466</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808196</v>
+        <v>124808177</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465573</v>
+        <v>465517</v>
       </c>
       <c r="R18" t="n">
-        <v>7054561</v>
+        <v>7054325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,6 +2433,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808186</v>
+        <v>124808176</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465644</v>
+        <v>465516</v>
       </c>
       <c r="R19" t="n">
-        <v>7054651</v>
+        <v>7054331</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808170</v>
+        <v>124808172</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465511</v>
+        <v>465497</v>
       </c>
       <c r="R20" t="n">
-        <v>7054408</v>
+        <v>7054413</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808201</v>
+        <v>124808168</v>
       </c>
       <c r="B21" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465645</v>
+        <v>465537</v>
       </c>
       <c r="R21" t="n">
-        <v>7054657</v>
+        <v>7054390</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2754,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808174</v>
+        <v>124808171</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465485</v>
+        <v>465504</v>
       </c>
       <c r="R22" t="n">
-        <v>7054334</v>
+        <v>7054411</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,7 +2892,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808181</v>
+        <v>124808165</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2927,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465621</v>
+        <v>465638</v>
       </c>
       <c r="R23" t="n">
-        <v>7054698</v>
+        <v>7054579</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808164</v>
+        <v>124808124</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465655</v>
+        <v>465636</v>
       </c>
       <c r="R24" t="n">
-        <v>7054664</v>
+        <v>7054718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,11 +3075,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808170</v>
+        <v>124808180</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465511</v>
+        <v>465470</v>
       </c>
       <c r="R2" t="n">
-        <v>7054408</v>
+        <v>7054306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808180</v>
+        <v>124808201</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465470</v>
+        <v>465645</v>
       </c>
       <c r="R3" t="n">
-        <v>7054306</v>
+        <v>7054657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808199</v>
+        <v>124808163</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465617</v>
+        <v>465656</v>
       </c>
       <c r="R4" t="n">
-        <v>7054717</v>
+        <v>7054667</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808196</v>
+        <v>124808198</v>
       </c>
       <c r="B5" t="n">
         <v>91030</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465573</v>
+        <v>465568</v>
       </c>
       <c r="R5" t="n">
-        <v>7054561</v>
+        <v>7054466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808174</v>
+        <v>124808197</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465485</v>
+        <v>465565</v>
       </c>
       <c r="R6" t="n">
-        <v>7054334</v>
+        <v>7054514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808167</v>
+        <v>124808196</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465559</v>
+        <v>465573</v>
       </c>
       <c r="R7" t="n">
-        <v>7054552</v>
+        <v>7054561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808163</v>
+        <v>124808165</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1352,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465656</v>
+        <v>465638</v>
       </c>
       <c r="R8" t="n">
-        <v>7054667</v>
+        <v>7054579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808173</v>
+        <v>124808167</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1459,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465503</v>
+        <v>465559</v>
       </c>
       <c r="R9" t="n">
-        <v>7054351</v>
+        <v>7054552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808164</v>
+        <v>124808186</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465655</v>
+        <v>465644</v>
       </c>
       <c r="R10" t="n">
-        <v>7054664</v>
+        <v>7054651</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808201</v>
+        <v>124808173</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465645</v>
+        <v>465503</v>
       </c>
       <c r="R11" t="n">
-        <v>7054657</v>
+        <v>7054351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808200</v>
+        <v>124808177</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465674</v>
+        <v>465517</v>
       </c>
       <c r="R12" t="n">
-        <v>7054729</v>
+        <v>7054325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808197</v>
+        <v>124808124</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465565</v>
+        <v>465636</v>
       </c>
       <c r="R13" t="n">
-        <v>7054514</v>
+        <v>7054718</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808169</v>
+        <v>124808176</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1979,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465536</v>
+        <v>465516</v>
       </c>
       <c r="R14" t="n">
-        <v>7054410</v>
+        <v>7054331</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2009,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808186</v>
+        <v>124808168</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465644</v>
+        <v>465537</v>
       </c>
       <c r="R15" t="n">
-        <v>7054651</v>
+        <v>7054390</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808181</v>
+        <v>124808199</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465621</v>
+        <v>465617</v>
       </c>
       <c r="R16" t="n">
-        <v>7054698</v>
+        <v>7054717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2223,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808198</v>
+        <v>124808171</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465568</v>
+        <v>465504</v>
       </c>
       <c r="R17" t="n">
-        <v>7054466</v>
+        <v>7054411</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2326,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808177</v>
+        <v>124808164</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465517</v>
+        <v>465655</v>
       </c>
       <c r="R18" t="n">
-        <v>7054325</v>
+        <v>7054664</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808176</v>
+        <v>124808174</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465516</v>
+        <v>465485</v>
       </c>
       <c r="R19" t="n">
-        <v>7054331</v>
+        <v>7054334</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808172</v>
+        <v>124808170</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465497</v>
+        <v>465511</v>
       </c>
       <c r="R20" t="n">
-        <v>7054413</v>
+        <v>7054408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808168</v>
+        <v>124808181</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465537</v>
+        <v>465621</v>
       </c>
       <c r="R21" t="n">
-        <v>7054390</v>
+        <v>7054698</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808171</v>
+        <v>124808172</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465504</v>
+        <v>465497</v>
       </c>
       <c r="R22" t="n">
-        <v>7054411</v>
+        <v>7054413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808165</v>
+        <v>124808200</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465638</v>
+        <v>465674</v>
       </c>
       <c r="R23" t="n">
-        <v>7054579</v>
+        <v>7054729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,11 +2968,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808124</v>
+        <v>124808169</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465636</v>
+        <v>465536</v>
       </c>
       <c r="R24" t="n">
-        <v>7054718</v>
+        <v>7054410</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3070,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808180</v>
+        <v>124808124</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465470</v>
+        <v>465636</v>
       </c>
       <c r="R2" t="n">
-        <v>7054306</v>
+        <v>7054718</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808163</v>
+        <v>124808186</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465656</v>
+        <v>465644</v>
       </c>
       <c r="R4" t="n">
-        <v>7054667</v>
+        <v>7054651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808198</v>
+        <v>124808181</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465568</v>
+        <v>465621</v>
       </c>
       <c r="R5" t="n">
-        <v>7054466</v>
+        <v>7054698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808197</v>
+        <v>124808164</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465565</v>
+        <v>465655</v>
       </c>
       <c r="R6" t="n">
-        <v>7054514</v>
+        <v>7054664</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808196</v>
+        <v>124808173</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465573</v>
+        <v>465503</v>
       </c>
       <c r="R7" t="n">
-        <v>7054561</v>
+        <v>7054351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808165</v>
+        <v>124808163</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465638</v>
+        <v>465656</v>
       </c>
       <c r="R8" t="n">
-        <v>7054579</v>
+        <v>7054667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808167</v>
+        <v>124808196</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465559</v>
+        <v>465573</v>
       </c>
       <c r="R9" t="n">
-        <v>7054552</v>
+        <v>7054561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808186</v>
+        <v>124808197</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465644</v>
+        <v>465565</v>
       </c>
       <c r="R10" t="n">
-        <v>7054651</v>
+        <v>7054514</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808173</v>
+        <v>124808199</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465503</v>
+        <v>465617</v>
       </c>
       <c r="R11" t="n">
-        <v>7054351</v>
+        <v>7054717</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808177</v>
+        <v>124808172</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465517</v>
+        <v>465497</v>
       </c>
       <c r="R12" t="n">
-        <v>7054325</v>
+        <v>7054413</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808124</v>
+        <v>124808200</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465636</v>
+        <v>465674</v>
       </c>
       <c r="R13" t="n">
-        <v>7054718</v>
+        <v>7054729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808176</v>
+        <v>124808174</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465516</v>
+        <v>465485</v>
       </c>
       <c r="R14" t="n">
-        <v>7054331</v>
+        <v>7054334</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808168</v>
+        <v>124808165</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465537</v>
+        <v>465638</v>
       </c>
       <c r="R15" t="n">
-        <v>7054390</v>
+        <v>7054579</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808199</v>
+        <v>124808177</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465617</v>
+        <v>465517</v>
       </c>
       <c r="R16" t="n">
-        <v>7054717</v>
+        <v>7054325</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808171</v>
+        <v>124808170</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465504</v>
+        <v>465511</v>
       </c>
       <c r="R17" t="n">
-        <v>7054411</v>
+        <v>7054408</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808164</v>
+        <v>124808168</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465655</v>
+        <v>465537</v>
       </c>
       <c r="R18" t="n">
-        <v>7054664</v>
+        <v>7054390</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808174</v>
+        <v>124808167</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465485</v>
+        <v>465559</v>
       </c>
       <c r="R19" t="n">
-        <v>7054334</v>
+        <v>7054552</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808170</v>
+        <v>124808180</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465511</v>
+        <v>465470</v>
       </c>
       <c r="R20" t="n">
-        <v>7054408</v>
+        <v>7054306</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808181</v>
+        <v>124808171</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465621</v>
+        <v>465504</v>
       </c>
       <c r="R21" t="n">
-        <v>7054698</v>
+        <v>7054411</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808172</v>
+        <v>124808176</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465497</v>
+        <v>465516</v>
       </c>
       <c r="R22" t="n">
-        <v>7054413</v>
+        <v>7054331</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808200</v>
+        <v>124808169</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465674</v>
+        <v>465536</v>
       </c>
       <c r="R23" t="n">
-        <v>7054729</v>
+        <v>7054410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,6 +2968,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808169</v>
+        <v>124808198</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465536</v>
+        <v>465568</v>
       </c>
       <c r="R24" t="n">
-        <v>7054410</v>
+        <v>7054466</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,11 +3075,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808124</v>
+        <v>124808169</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465636</v>
+        <v>465536</v>
       </c>
       <c r="R2" t="n">
-        <v>7054718</v>
+        <v>7054410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808201</v>
+        <v>124808198</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465645</v>
+        <v>465568</v>
       </c>
       <c r="R3" t="n">
-        <v>7054657</v>
+        <v>7054466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808186</v>
+        <v>124808176</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465644</v>
+        <v>465516</v>
       </c>
       <c r="R4" t="n">
-        <v>7054651</v>
+        <v>7054331</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808181</v>
+        <v>124808164</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465621</v>
+        <v>465655</v>
       </c>
       <c r="R5" t="n">
-        <v>7054698</v>
+        <v>7054664</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808164</v>
+        <v>124808197</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465655</v>
+        <v>465565</v>
       </c>
       <c r="R6" t="n">
-        <v>7054664</v>
+        <v>7054514</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808173</v>
+        <v>124808186</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465503</v>
+        <v>465644</v>
       </c>
       <c r="R7" t="n">
-        <v>7054351</v>
+        <v>7054651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808163</v>
+        <v>124808171</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465656</v>
+        <v>465504</v>
       </c>
       <c r="R8" t="n">
-        <v>7054667</v>
+        <v>7054411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808196</v>
+        <v>124808174</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465573</v>
+        <v>465485</v>
       </c>
       <c r="R9" t="n">
-        <v>7054561</v>
+        <v>7054334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808197</v>
+        <v>124808196</v>
       </c>
       <c r="B10" t="n">
         <v>91030</v>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465565</v>
+        <v>465573</v>
       </c>
       <c r="R10" t="n">
-        <v>7054514</v>
+        <v>7054561</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808199</v>
+        <v>124808180</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465617</v>
+        <v>465470</v>
       </c>
       <c r="R11" t="n">
-        <v>7054717</v>
+        <v>7054306</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808172</v>
+        <v>124808170</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465497</v>
+        <v>465511</v>
       </c>
       <c r="R12" t="n">
-        <v>7054413</v>
+        <v>7054408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,7 +1934,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808174</v>
+        <v>124808167</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465485</v>
+        <v>465559</v>
       </c>
       <c r="R14" t="n">
-        <v>7054334</v>
+        <v>7054552</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808177</v>
+        <v>124808181</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2183,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465517</v>
+        <v>465621</v>
       </c>
       <c r="R16" t="n">
-        <v>7054325</v>
+        <v>7054698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808170</v>
+        <v>124808201</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465511</v>
+        <v>465645</v>
       </c>
       <c r="R17" t="n">
-        <v>7054408</v>
+        <v>7054657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2331,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808168</v>
+        <v>124808173</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465537</v>
+        <v>465503</v>
       </c>
       <c r="R18" t="n">
-        <v>7054390</v>
+        <v>7054351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808167</v>
+        <v>124808177</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465559</v>
+        <v>465517</v>
       </c>
       <c r="R19" t="n">
-        <v>7054552</v>
+        <v>7054325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808180</v>
+        <v>124808163</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465470</v>
+        <v>465656</v>
       </c>
       <c r="R20" t="n">
-        <v>7054306</v>
+        <v>7054667</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2678,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808171</v>
+        <v>124808172</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465504</v>
+        <v>465497</v>
       </c>
       <c r="R21" t="n">
-        <v>7054411</v>
+        <v>7054413</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808176</v>
+        <v>124808199</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2801,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465516</v>
+        <v>465617</v>
       </c>
       <c r="R22" t="n">
-        <v>7054331</v>
+        <v>7054717</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808169</v>
+        <v>124808124</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465536</v>
+        <v>465636</v>
       </c>
       <c r="R23" t="n">
-        <v>7054410</v>
+        <v>7054718</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,11 +2968,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808198</v>
+        <v>124808168</v>
       </c>
       <c r="B24" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465568</v>
+        <v>465537</v>
       </c>
       <c r="R24" t="n">
-        <v>7054466</v>
+        <v>7054390</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3070,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808169</v>
+        <v>124808165</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465536</v>
+        <v>465638</v>
       </c>
       <c r="R2" t="n">
-        <v>7054410</v>
+        <v>7054579</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808198</v>
+        <v>124808173</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465568</v>
+        <v>465503</v>
       </c>
       <c r="R3" t="n">
-        <v>7054466</v>
+        <v>7054351</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808176</v>
+        <v>124808181</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465516</v>
+        <v>465621</v>
       </c>
       <c r="R4" t="n">
-        <v>7054331</v>
+        <v>7054698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808164</v>
+        <v>124808169</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465655</v>
+        <v>465536</v>
       </c>
       <c r="R5" t="n">
-        <v>7054664</v>
+        <v>7054410</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808197</v>
+        <v>124808201</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>88359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465565</v>
+        <v>465645</v>
       </c>
       <c r="R6" t="n">
-        <v>7054514</v>
+        <v>7054657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808186</v>
+        <v>124808164</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465644</v>
+        <v>465655</v>
       </c>
       <c r="R7" t="n">
-        <v>7054651</v>
+        <v>7054664</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808171</v>
+        <v>124808197</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465504</v>
+        <v>465565</v>
       </c>
       <c r="R8" t="n">
-        <v>7054411</v>
+        <v>7054514</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808174</v>
+        <v>124808163</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465485</v>
+        <v>465656</v>
       </c>
       <c r="R9" t="n">
-        <v>7054334</v>
+        <v>7054667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808196</v>
+        <v>124808124</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465573</v>
+        <v>465636</v>
       </c>
       <c r="R10" t="n">
-        <v>7054561</v>
+        <v>7054718</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808180</v>
+        <v>124808171</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465470</v>
+        <v>465504</v>
       </c>
       <c r="R11" t="n">
-        <v>7054306</v>
+        <v>7054411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808170</v>
+        <v>124808167</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465511</v>
+        <v>465559</v>
       </c>
       <c r="R12" t="n">
-        <v>7054408</v>
+        <v>7054552</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808200</v>
+        <v>124808186</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465674</v>
+        <v>465644</v>
       </c>
       <c r="R13" t="n">
-        <v>7054729</v>
+        <v>7054651</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808167</v>
+        <v>124808180</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465559</v>
+        <v>465470</v>
       </c>
       <c r="R14" t="n">
-        <v>7054552</v>
+        <v>7054306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808165</v>
+        <v>124808177</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2081,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465638</v>
+        <v>465517</v>
       </c>
       <c r="R15" t="n">
-        <v>7054579</v>
+        <v>7054325</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808181</v>
+        <v>124808198</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465621</v>
+        <v>465568</v>
       </c>
       <c r="R16" t="n">
-        <v>7054698</v>
+        <v>7054466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,11 +2229,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808201</v>
+        <v>124808172</v>
       </c>
       <c r="B17" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465645</v>
+        <v>465497</v>
       </c>
       <c r="R17" t="n">
-        <v>7054657</v>
+        <v>7054413</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,6 +2331,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808173</v>
+        <v>124808174</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2397,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465503</v>
+        <v>465485</v>
       </c>
       <c r="R18" t="n">
-        <v>7054351</v>
+        <v>7054334</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2442,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808177</v>
+        <v>124808176</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2504,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465517</v>
+        <v>465516</v>
       </c>
       <c r="R19" t="n">
-        <v>7054325</v>
+        <v>7054331</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2544,7 +2549,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808163</v>
+        <v>124808170</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465656</v>
+        <v>465511</v>
       </c>
       <c r="R20" t="n">
-        <v>7054667</v>
+        <v>7054408</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2678,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808172</v>
+        <v>124808168</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2718,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465497</v>
+        <v>465537</v>
       </c>
       <c r="R21" t="n">
-        <v>7054413</v>
+        <v>7054390</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808199</v>
+        <v>124808196</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465617</v>
+        <v>465573</v>
       </c>
       <c r="R22" t="n">
-        <v>7054717</v>
+        <v>7054561</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,11 +2866,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808124</v>
+        <v>124808199</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465636</v>
+        <v>465617</v>
       </c>
       <c r="R23" t="n">
-        <v>7054718</v>
+        <v>7054717</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,6 +2968,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808168</v>
+        <v>124808200</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465537</v>
+        <v>465674</v>
       </c>
       <c r="R24" t="n">
-        <v>7054390</v>
+        <v>7054729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,11 +3075,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808165</v>
+        <v>124808201</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465638</v>
+        <v>465645</v>
       </c>
       <c r="R2" t="n">
-        <v>7054579</v>
+        <v>7054657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808173</v>
+        <v>124808176</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465503</v>
+        <v>465516</v>
       </c>
       <c r="R3" t="n">
-        <v>7054351</v>
+        <v>7054331</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808181</v>
+        <v>124808164</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465621</v>
+        <v>465655</v>
       </c>
       <c r="R4" t="n">
-        <v>7054698</v>
+        <v>7054664</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808169</v>
+        <v>124808180</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465536</v>
+        <v>465470</v>
       </c>
       <c r="R5" t="n">
-        <v>7054410</v>
+        <v>7054306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808201</v>
+        <v>124808167</v>
       </c>
       <c r="B6" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465645</v>
+        <v>465559</v>
       </c>
       <c r="R6" t="n">
-        <v>7054657</v>
+        <v>7054552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808164</v>
+        <v>124808186</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465655</v>
+        <v>465644</v>
       </c>
       <c r="R7" t="n">
-        <v>7054664</v>
+        <v>7054651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808197</v>
+        <v>124808174</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465565</v>
+        <v>465485</v>
       </c>
       <c r="R8" t="n">
-        <v>7054514</v>
+        <v>7054334</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808163</v>
+        <v>124808198</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465656</v>
+        <v>465568</v>
       </c>
       <c r="R9" t="n">
-        <v>7054667</v>
+        <v>7054466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808171</v>
+        <v>124808163</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465504</v>
+        <v>465656</v>
       </c>
       <c r="R11" t="n">
-        <v>7054411</v>
+        <v>7054667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808167</v>
+        <v>124808171</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465559</v>
+        <v>465504</v>
       </c>
       <c r="R12" t="n">
-        <v>7054552</v>
+        <v>7054411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808186</v>
+        <v>124808172</v>
       </c>
       <c r="B13" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465644</v>
+        <v>465497</v>
       </c>
       <c r="R13" t="n">
-        <v>7054651</v>
+        <v>7054413</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808180</v>
+        <v>124808173</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465470</v>
+        <v>465503</v>
       </c>
       <c r="R14" t="n">
-        <v>7054306</v>
+        <v>7054351</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808177</v>
+        <v>124808197</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465517</v>
+        <v>465565</v>
       </c>
       <c r="R15" t="n">
-        <v>7054325</v>
+        <v>7054514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808198</v>
+        <v>124808199</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465568</v>
+        <v>465617</v>
       </c>
       <c r="R16" t="n">
-        <v>7054466</v>
+        <v>7054717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,6 +2224,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808172</v>
+        <v>124808165</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465497</v>
+        <v>465638</v>
       </c>
       <c r="R17" t="n">
-        <v>7054413</v>
+        <v>7054579</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808174</v>
+        <v>124808168</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465485</v>
+        <v>465537</v>
       </c>
       <c r="R18" t="n">
-        <v>7054334</v>
+        <v>7054390</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,7 +2469,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808176</v>
+        <v>124808170</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465516</v>
+        <v>465511</v>
       </c>
       <c r="R19" t="n">
-        <v>7054331</v>
+        <v>7054408</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808170</v>
+        <v>124808169</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465511</v>
+        <v>465536</v>
       </c>
       <c r="R20" t="n">
-        <v>7054408</v>
+        <v>7054410</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,7 +2683,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808168</v>
+        <v>124808181</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465537</v>
+        <v>465621</v>
       </c>
       <c r="R21" t="n">
-        <v>7054390</v>
+        <v>7054698</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808199</v>
+        <v>124808200</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465617</v>
+        <v>465674</v>
       </c>
       <c r="R23" t="n">
-        <v>7054717</v>
+        <v>7054729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,11 +2968,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808200</v>
+        <v>124808177</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465674</v>
+        <v>465517</v>
       </c>
       <c r="R24" t="n">
-        <v>7054729</v>
+        <v>7054325</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3070,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808186</v>
+        <v>124808198</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465644</v>
+        <v>465568</v>
       </c>
       <c r="R7" t="n">
-        <v>7054651</v>
+        <v>7054466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808174</v>
+        <v>124808186</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465485</v>
+        <v>465644</v>
       </c>
       <c r="R8" t="n">
-        <v>7054334</v>
+        <v>7054651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808198</v>
+        <v>124808174</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465568</v>
+        <v>465485</v>
       </c>
       <c r="R9" t="n">
-        <v>7054466</v>
+        <v>7054334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2790,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808196</v>
+        <v>124808177</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2830,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465573</v>
+        <v>465517</v>
       </c>
       <c r="R22" t="n">
-        <v>7054561</v>
+        <v>7054325</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,6 +2866,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808200</v>
+        <v>124808196</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2913,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2937,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465674</v>
+        <v>465573</v>
       </c>
       <c r="R23" t="n">
-        <v>7054729</v>
+        <v>7054561</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2994,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808177</v>
+        <v>124808200</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465517</v>
+        <v>465674</v>
       </c>
       <c r="R24" t="n">
-        <v>7054325</v>
+        <v>7054729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,11 +3075,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808201</v>
+        <v>124808173</v>
       </c>
       <c r="B2" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465645</v>
+        <v>465503</v>
       </c>
       <c r="R2" t="n">
-        <v>7054657</v>
+        <v>7054351</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808176</v>
+        <v>124808196</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465516</v>
+        <v>465573</v>
       </c>
       <c r="R3" t="n">
-        <v>7054331</v>
+        <v>7054561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808164</v>
+        <v>124808165</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465655</v>
+        <v>465638</v>
       </c>
       <c r="R4" t="n">
-        <v>7054664</v>
+        <v>7054579</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808180</v>
+        <v>124808199</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465470</v>
+        <v>465617</v>
       </c>
       <c r="R5" t="n">
-        <v>7054306</v>
+        <v>7054717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808167</v>
+        <v>124808169</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465559</v>
+        <v>465536</v>
       </c>
       <c r="R6" t="n">
-        <v>7054552</v>
+        <v>7054410</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808198</v>
+        <v>124808171</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465568</v>
+        <v>465504</v>
       </c>
       <c r="R7" t="n">
-        <v>7054466</v>
+        <v>7054411</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808186</v>
+        <v>124808124</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465644</v>
+        <v>465636</v>
       </c>
       <c r="R8" t="n">
-        <v>7054651</v>
+        <v>7054718</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808174</v>
+        <v>124808180</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465485</v>
+        <v>465470</v>
       </c>
       <c r="R9" t="n">
-        <v>7054334</v>
+        <v>7054306</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808124</v>
+        <v>124808181</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465636</v>
+        <v>465621</v>
       </c>
       <c r="R10" t="n">
-        <v>7054718</v>
+        <v>7054698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808163</v>
+        <v>124808201</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465656</v>
+        <v>465645</v>
       </c>
       <c r="R11" t="n">
-        <v>7054667</v>
+        <v>7054657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808171</v>
+        <v>124808170</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465504</v>
+        <v>465511</v>
       </c>
       <c r="R12" t="n">
-        <v>7054411</v>
+        <v>7054408</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808172</v>
+        <v>124808198</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465497</v>
+        <v>465568</v>
       </c>
       <c r="R13" t="n">
-        <v>7054413</v>
+        <v>7054466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1913,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808173</v>
+        <v>124808197</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465503</v>
+        <v>465565</v>
       </c>
       <c r="R14" t="n">
-        <v>7054351</v>
+        <v>7054514</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,11 +2015,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808197</v>
+        <v>124808174</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465565</v>
+        <v>465485</v>
       </c>
       <c r="R15" t="n">
-        <v>7054514</v>
+        <v>7054334</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2117,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808199</v>
+        <v>124808167</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465617</v>
+        <v>465559</v>
       </c>
       <c r="R16" t="n">
-        <v>7054717</v>
+        <v>7054552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808165</v>
+        <v>124808176</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465638</v>
+        <v>465516</v>
       </c>
       <c r="R17" t="n">
-        <v>7054579</v>
+        <v>7054331</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808168</v>
+        <v>124808163</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465537</v>
+        <v>465656</v>
       </c>
       <c r="R18" t="n">
-        <v>7054390</v>
+        <v>7054667</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808170</v>
+        <v>124808186</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465511</v>
+        <v>465644</v>
       </c>
       <c r="R19" t="n">
-        <v>7054408</v>
+        <v>7054651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,11 +2545,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808169</v>
+        <v>124808200</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465536</v>
+        <v>465674</v>
       </c>
       <c r="R20" t="n">
-        <v>7054410</v>
+        <v>7054729</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,11 +2647,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808181</v>
+        <v>124808177</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2723,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465621</v>
+        <v>465517</v>
       </c>
       <c r="R21" t="n">
-        <v>7054698</v>
+        <v>7054325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2753,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2790,7 +2780,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808177</v>
+        <v>124808172</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2830,10 +2820,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465517</v>
+        <v>465497</v>
       </c>
       <c r="R22" t="n">
-        <v>7054325</v>
+        <v>7054413</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,7 +2860,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2897,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808196</v>
+        <v>124808168</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,21 +2903,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465573</v>
+        <v>465537</v>
       </c>
       <c r="R23" t="n">
-        <v>7054561</v>
+        <v>7054390</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,6 +2963,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808200</v>
+        <v>124808164</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465674</v>
+        <v>465655</v>
       </c>
       <c r="R24" t="n">
-        <v>7054729</v>
+        <v>7054664</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3070,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808173</v>
+        <v>124808180</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465503</v>
+        <v>465470</v>
       </c>
       <c r="R2" t="n">
-        <v>7054351</v>
+        <v>7054306</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808196</v>
+        <v>124808198</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465573</v>
+        <v>465568</v>
       </c>
       <c r="R3" t="n">
-        <v>7054561</v>
+        <v>7054466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808165</v>
+        <v>124808167</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465638</v>
+        <v>465559</v>
       </c>
       <c r="R4" t="n">
-        <v>7054579</v>
+        <v>7054552</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808199</v>
+        <v>124808186</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91162</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465617</v>
+        <v>465644</v>
       </c>
       <c r="R5" t="n">
-        <v>7054717</v>
+        <v>7054651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808169</v>
+        <v>124808165</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465536</v>
+        <v>465638</v>
       </c>
       <c r="R6" t="n">
-        <v>7054410</v>
+        <v>7054579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808171</v>
+        <v>124808173</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465504</v>
+        <v>465503</v>
       </c>
       <c r="R7" t="n">
-        <v>7054411</v>
+        <v>7054351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808124</v>
+        <v>124808181</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465636</v>
+        <v>465621</v>
       </c>
       <c r="R8" t="n">
-        <v>7054718</v>
+        <v>7054698</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808180</v>
+        <v>124808174</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465470</v>
+        <v>465485</v>
       </c>
       <c r="R9" t="n">
-        <v>7054306</v>
+        <v>7054334</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808181</v>
+        <v>124808172</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465621</v>
+        <v>465497</v>
       </c>
       <c r="R10" t="n">
-        <v>7054698</v>
+        <v>7054413</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808201</v>
+        <v>124808176</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465645</v>
+        <v>465516</v>
       </c>
       <c r="R11" t="n">
-        <v>7054657</v>
+        <v>7054331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1704,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808170</v>
+        <v>124808196</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465511</v>
+        <v>465573</v>
       </c>
       <c r="R12" t="n">
-        <v>7054408</v>
+        <v>7054561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808198</v>
+        <v>124808201</v>
       </c>
       <c r="B13" t="n">
-        <v>91030</v>
+        <v>88512</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465568</v>
+        <v>465645</v>
       </c>
       <c r="R13" t="n">
-        <v>7054466</v>
+        <v>7054657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1939,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808197</v>
+        <v>124808177</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465565</v>
+        <v>465517</v>
       </c>
       <c r="R14" t="n">
-        <v>7054514</v>
+        <v>7054325</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,6 +2015,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808174</v>
+        <v>124808124</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465485</v>
+        <v>465636</v>
       </c>
       <c r="R15" t="n">
-        <v>7054334</v>
+        <v>7054718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2122,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808167</v>
+        <v>124808200</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465559</v>
+        <v>465674</v>
       </c>
       <c r="R16" t="n">
-        <v>7054552</v>
+        <v>7054729</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,11 +2224,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808176</v>
+        <v>124808171</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465516</v>
+        <v>465504</v>
       </c>
       <c r="R17" t="n">
-        <v>7054331</v>
+        <v>7054411</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808163</v>
+        <v>124808164</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465656</v>
+        <v>465655</v>
       </c>
       <c r="R18" t="n">
-        <v>7054667</v>
+        <v>7054664</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808186</v>
+        <v>124808163</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465644</v>
+        <v>465656</v>
       </c>
       <c r="R19" t="n">
-        <v>7054651</v>
+        <v>7054667</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808200</v>
+        <v>124808168</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465674</v>
+        <v>465537</v>
       </c>
       <c r="R20" t="n">
-        <v>7054729</v>
+        <v>7054390</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,6 +2647,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808177</v>
+        <v>124808199</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465517</v>
+        <v>465617</v>
       </c>
       <c r="R21" t="n">
-        <v>7054325</v>
+        <v>7054717</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,7 +2758,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2780,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808172</v>
+        <v>124808169</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465497</v>
+        <v>465536</v>
       </c>
       <c r="R22" t="n">
-        <v>7054413</v>
+        <v>7054410</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,7 +2865,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808168</v>
+        <v>124808197</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2903,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465537</v>
+        <v>465565</v>
       </c>
       <c r="R23" t="n">
-        <v>7054390</v>
+        <v>7054514</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,11 +2968,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808164</v>
+        <v>124808170</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465655</v>
+        <v>465511</v>
       </c>
       <c r="R24" t="n">
-        <v>7054664</v>
+        <v>7054408</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124808173</v>
+        <v>124808181</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465503</v>
+        <v>465621</v>
       </c>
       <c r="R7" t="n">
-        <v>7054351</v>
+        <v>7054698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808181</v>
+        <v>124808173</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465621</v>
+        <v>465503</v>
       </c>
       <c r="R8" t="n">
-        <v>7054698</v>
+        <v>7054351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808196</v>
+        <v>124808201</v>
       </c>
       <c r="B12" t="n">
-        <v>91184</v>
+        <v>88512</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465573</v>
+        <v>465645</v>
       </c>
       <c r="R12" t="n">
-        <v>7054561</v>
+        <v>7054657</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808201</v>
+        <v>124808196</v>
       </c>
       <c r="B13" t="n">
-        <v>88512</v>
+        <v>91184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465645</v>
+        <v>465573</v>
       </c>
       <c r="R13" t="n">
-        <v>7054657</v>
+        <v>7054561</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808197</v>
+        <v>124808170</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465565</v>
+        <v>465511</v>
       </c>
       <c r="R23" t="n">
-        <v>7054514</v>
+        <v>7054408</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,6 +2968,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2994,10 +2999,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808170</v>
+        <v>124808197</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3010,21 +3015,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3034,10 +3039,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465511</v>
+        <v>465565</v>
       </c>
       <c r="R24" t="n">
-        <v>7054408</v>
+        <v>7054514</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,11 +3075,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124808180</v>
+        <v>124808169</v>
       </c>
       <c r="B2" t="n">
         <v>57635</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465470</v>
+        <v>465536</v>
       </c>
       <c r="R2" t="n">
-        <v>7054306</v>
+        <v>7054410</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124808198</v>
+        <v>124808186</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>91162</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465568</v>
+        <v>465644</v>
       </c>
       <c r="R3" t="n">
-        <v>7054466</v>
+        <v>7054651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124808167</v>
+        <v>124808170</v>
       </c>
       <c r="B4" t="n">
         <v>57635</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465559</v>
+        <v>465511</v>
       </c>
       <c r="R4" t="n">
-        <v>7054552</v>
+        <v>7054408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124808186</v>
+        <v>124808197</v>
       </c>
       <c r="B5" t="n">
-        <v>91162</v>
+        <v>91184</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465644</v>
+        <v>465565</v>
       </c>
       <c r="R5" t="n">
-        <v>7054651</v>
+        <v>7054514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124808165</v>
+        <v>124808172</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465638</v>
+        <v>465497</v>
       </c>
       <c r="R6" t="n">
-        <v>7054579</v>
+        <v>7054413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124808173</v>
+        <v>124808171</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465503</v>
+        <v>465504</v>
       </c>
       <c r="R8" t="n">
-        <v>7054351</v>
+        <v>7054411</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124808174</v>
+        <v>124808176</v>
       </c>
       <c r="B9" t="n">
         <v>57635</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465485</v>
+        <v>465516</v>
       </c>
       <c r="R9" t="n">
-        <v>7054334</v>
+        <v>7054331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124808172</v>
+        <v>124808177</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465497</v>
+        <v>465517</v>
       </c>
       <c r="R10" t="n">
-        <v>7054413</v>
+        <v>7054325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124808176</v>
+        <v>124808167</v>
       </c>
       <c r="B11" t="n">
         <v>57635</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465516</v>
+        <v>465559</v>
       </c>
       <c r="R11" t="n">
-        <v>7054331</v>
+        <v>7054552</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124808201</v>
+        <v>124808173</v>
       </c>
       <c r="B12" t="n">
-        <v>88512</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465645</v>
+        <v>465503</v>
       </c>
       <c r="R12" t="n">
-        <v>7054657</v>
+        <v>7054351</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124808196</v>
+        <v>124808164</v>
       </c>
       <c r="B13" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465573</v>
+        <v>465655</v>
       </c>
       <c r="R13" t="n">
-        <v>7054561</v>
+        <v>7054664</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,6 +1918,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124808177</v>
+        <v>124808180</v>
       </c>
       <c r="B14" t="n">
         <v>57635</v>
@@ -1979,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465517</v>
+        <v>465470</v>
       </c>
       <c r="R14" t="n">
-        <v>7054325</v>
+        <v>7054306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124808124</v>
+        <v>124808201</v>
       </c>
       <c r="B15" t="n">
-        <v>91166</v>
+        <v>88512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465636</v>
+        <v>465645</v>
       </c>
       <c r="R15" t="n">
-        <v>7054718</v>
+        <v>7054657</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124808200</v>
+        <v>124808165</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465674</v>
+        <v>465638</v>
       </c>
       <c r="R16" t="n">
-        <v>7054729</v>
+        <v>7054579</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808171</v>
+        <v>124808196</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465504</v>
+        <v>465573</v>
       </c>
       <c r="R17" t="n">
-        <v>7054411</v>
+        <v>7054561</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808164</v>
+        <v>124808168</v>
       </c>
       <c r="B18" t="n">
         <v>57635</v>
@@ -2397,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465655</v>
+        <v>465537</v>
       </c>
       <c r="R18" t="n">
-        <v>7054664</v>
+        <v>7054390</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808163</v>
+        <v>124808200</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2490,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465656</v>
+        <v>465674</v>
       </c>
       <c r="R19" t="n">
-        <v>7054667</v>
+        <v>7054729</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2550,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2576,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124808168</v>
+        <v>124808199</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2592,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465537</v>
+        <v>465617</v>
       </c>
       <c r="R20" t="n">
-        <v>7054390</v>
+        <v>7054717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2656,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124808199</v>
+        <v>124808174</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2699,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465617</v>
+        <v>465485</v>
       </c>
       <c r="R21" t="n">
-        <v>7054717</v>
+        <v>7054334</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2758,7 +2763,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2785,10 +2790,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124808169</v>
+        <v>124808124</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2801,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465536</v>
+        <v>465636</v>
       </c>
       <c r="R22" t="n">
-        <v>7054410</v>
+        <v>7054718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,11 +2866,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124808170</v>
+        <v>124808198</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2908,21 +2908,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>465511</v>
+        <v>465568</v>
       </c>
       <c r="R23" t="n">
-        <v>7054408</v>
+        <v>7054466</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2968,11 +2968,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2999,10 +2994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124808197</v>
+        <v>124808163</v>
       </c>
       <c r="B24" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3015,21 +3010,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3039,10 +3034,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465565</v>
+        <v>465656</v>
       </c>
       <c r="R24" t="n">
-        <v>7054514</v>
+        <v>7054667</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,6 +3070,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124808196</v>
+        <v>124808200</v>
       </c>
       <c r="B17" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465573</v>
+        <v>465674</v>
       </c>
       <c r="R17" t="n">
-        <v>7054561</v>
+        <v>7054729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124808168</v>
+        <v>124808196</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465537</v>
+        <v>465573</v>
       </c>
       <c r="R18" t="n">
-        <v>7054390</v>
+        <v>7054561</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,11 +2443,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124808200</v>
+        <v>124808168</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2514,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465674</v>
+        <v>465537</v>
       </c>
       <c r="R19" t="n">
-        <v>7054729</v>
+        <v>7054390</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,6 +2545,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124808169</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>124808170</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>124808172</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>124808181</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>124808171</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>124808176</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>124808177</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>124808167</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>124808173</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>124808164</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>124808180</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>124808165</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>124808168</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>124808174</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>124808163</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124808169</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>124808170</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>124808172</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>124808181</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>124808171</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>124808176</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>124808177</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>124808167</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>124808173</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>124808164</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>124808180</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>124808165</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>124808168</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>124808174</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>124808163</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 22511-2021 artfynd.xlsx
+++ b/artfynd/A 22511-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124808169</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>124808170</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>124808172</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>124808181</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>124808171</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>124808176</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>124808177</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>124808167</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>124808173</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>124808164</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>124808180</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>124808165</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>124808168</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>124808174</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>124808163</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
